--- a/sheets/대금율보/검수/엘빔보.xlsx
+++ b/sheets/대금율보/검수/엘빔보.xlsx
@@ -4796,14 +4796,14 @@
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 南無</t>
         </is>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㶂</t>
         </is>
       </c>
@@ -4817,7 +4817,7 @@
       <c r="G4" s="25"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4831,7 +4831,7 @@
       <c r="K4" s="25"/>
       <c r="L4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4909,28 +4909,28 @@
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林南</t>
         </is>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋湳</t>
         </is>
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -4944,7 +4944,7 @@
       <c r="K6" s="27"/>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5022,7 +5022,7 @@
       <c r="C8" s="25"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳潕</t>
         </is>
       </c>
@@ -5031,28 +5031,28 @@
       <c r="G8" s="25"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5125,7 +5125,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潕潢</t>
         </is>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋湳</t>
         </is>
       </c>
@@ -5325,7 +5325,7 @@
       <c r="G14" s="27"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 浹</t>
         </is>
       </c>
@@ -5416,28 +5416,28 @@
       <c r="C16" s="25"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢汰</t>
         </is>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
       <c r="I16" s="24"/>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -5451,7 +5451,7 @@
       <c r="M16" s="25"/>
       <c r="N16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -5520,7 +5520,7 @@
       <c r="E18" s="27"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -5529,7 +5529,7 @@
       <c r="I18" s="27"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>
@@ -5543,7 +5543,7 @@
       <c r="M18" s="27"/>
       <c r="N18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋</t>
         </is>
       </c>

--- a/sheets/대금율보/검수/엘빔보.xlsx
+++ b/sheets/대금율보/검수/엘빔보.xlsx
@@ -4696,28 +4696,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Q5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Q6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="Q8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Q9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="Q10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="Q14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -5459,7 +5459,7 @@
       <c r="P16" s="21"/>
       <c r="Q16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -5503,7 +5503,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5557,6 +5557,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>